--- a/web_scraping-positly/data/links.xlsx
+++ b/web_scraping-positly/data/links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1B9C6C-7944-4BE6-A025-A487C3B20CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA28B25-96CB-4D46-AE09-FE6B5E92B4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="83">
-  <si>
-    <t>https://psychology.fas.harvard.edu/people?search=&amp;page=0 - </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="82">
   <si>
     <t>https://psychology.fas.harvard.edu/fellows-and-associates</t>
   </si>
@@ -231,9 +228,6 @@
     <t>https://psych.indiana.edu/directory/administration/index.html</t>
   </si>
   <si>
-    <t>Universidad Nacional Autónoma de México (UNAM)</t>
-  </si>
-  <si>
     <t>https://hhs.purdue.edu/about-hhs/directory/?staff_faculty_type=Faculty&amp;hhs_department_staff=Department%20of%20Psychological%20Sciences</t>
   </si>
   <si>
@@ -249,9 +243,6 @@
     <t>https://www.pcs.tsinghua.edu.cn/xlxen/Faculty/Current_Faculty/Associate_Professors.htm</t>
   </si>
   <si>
-    <t>https://www.pcs.tsinghua.edu.cn/xlxen/Faculty/Current_Faculty/Professors.htm#</t>
-  </si>
-  <si>
     <t>https://www.pcs.tsinghua.edu.cn/xlxen/Faculty/Current_Faculty.htm</t>
   </si>
   <si>
@@ -274,6 +265,12 @@
   </si>
   <si>
     <t>https://www.polyu.edu.hk/apss/people/academic-staff/</t>
+  </si>
+  <si>
+    <t>https://psychology.fas.harvard.edu/people?search=&amp;page=0</t>
+  </si>
+  <si>
+    <t>https://www.pcs.tsinghua.edu.cn/xlxen/Faculty/Current_Faculty/Professors.htm</t>
   </si>
 </sst>
 </file>
@@ -640,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A87"/>
+  <dimension ref="A1:A85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="89.42578125" customWidth="1"/>
@@ -648,22 +645,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
@@ -702,12 +699,12 @@
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -722,12 +719,12 @@
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -923,16 +920,16 @@
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="4" t="s">
         <v>55</v>
       </c>
     </row>
@@ -952,22 +949,22 @@
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="3" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="5" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="4" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="3" t="s">
         <v>62</v>
       </c>
     </row>
@@ -992,7 +989,7 @@
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="4" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1002,12 +999,12 @@
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="4" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1017,18 +1014,18 @@
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="4" t="s">
-        <v>72</v>
+      <c r="A75" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
@@ -1038,107 +1035,98 @@
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>82</v>
+      <c r="A85" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" display="https://psychology.fas.harvard.edu/people?search=&amp;page=0" xr:uid="{23BF9EF3-767C-4DAF-B92F-C39BA79C0524}"/>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{23BF9EF3-767C-4DAF-B92F-C39BA79C0524}"/>
     <hyperlink ref="A2" r:id="rId2" xr:uid="{26DE35FD-C3FE-4F53-9D06-91378036D91A}"/>
     <hyperlink ref="A3" r:id="rId3" xr:uid="{321A08B4-5092-4AF5-83CA-C6225EB9DE4D}"/>
-    <hyperlink ref="A4" r:id="rId4" xr:uid="{4AAB144C-890F-4B77-B2E1-4770B70A5AF7}"/>
-    <hyperlink ref="A5" r:id="rId5" xr:uid="{4CB9E738-C2A3-4A0B-A76A-2BA6A3C71A0A}"/>
-    <hyperlink ref="A6" r:id="rId6" xr:uid="{808033F4-D4E3-455C-826E-285C2E7B7559}"/>
-    <hyperlink ref="A7" r:id="rId7" xr:uid="{CBDC038C-2AB8-4C78-927A-82ABF153C1F9}"/>
-    <hyperlink ref="A8" r:id="rId8" xr:uid="{33304A3B-055F-4AB5-BDE5-93C50D0B5A09}"/>
-    <hyperlink ref="A9" r:id="rId9" xr:uid="{A653D656-96D2-4E8B-A351-C084C18A7C41}"/>
-    <hyperlink ref="A10" r:id="rId10" xr:uid="{31A508E0-5F90-49AE-B561-5977B5C4F4CC}"/>
-    <hyperlink ref="A11" r:id="rId11" xr:uid="{69EFF606-7E4E-4758-8FBA-56C60A1C1E11}"/>
-    <hyperlink ref="A12" r:id="rId12" xr:uid="{B7A286A9-5428-4ACD-AB67-D0D27D4FF4B6}"/>
-    <hyperlink ref="A14" r:id="rId13" xr:uid="{D38AFE28-5C63-4B2A-9DE0-380E7FFAB029}"/>
-    <hyperlink ref="A15" r:id="rId14" xr:uid="{E690C1ED-6E53-467F-ADB5-85839B2A02C8}"/>
-    <hyperlink ref="A16" r:id="rId15" xr:uid="{FD31BAA3-A23D-488F-9251-4E9B3F823D1F}"/>
-    <hyperlink ref="A18" r:id="rId16" xr:uid="{E8734ADA-CBCA-4424-AB2A-4EF369BF37DC}"/>
-    <hyperlink ref="A19" r:id="rId17" xr:uid="{96D758A5-3ADE-45D8-9D94-184A169418CD}"/>
-    <hyperlink ref="A20" r:id="rId18" xr:uid="{7E513055-D324-4218-A278-3A0D89815E79}"/>
-    <hyperlink ref="A21" r:id="rId19" xr:uid="{45E02E90-651D-4B0F-894D-CC328F64B669}"/>
-    <hyperlink ref="A22" r:id="rId20" xr:uid="{D07FA495-029B-4B56-98E8-3D576F284893}"/>
-    <hyperlink ref="A23" r:id="rId21" xr:uid="{7E524225-DFAE-4D69-91F9-F781B31234C1}"/>
-    <hyperlink ref="A24" r:id="rId22" xr:uid="{FF41D14E-E8D4-4578-A644-05CC79649038}"/>
-    <hyperlink ref="A25" r:id="rId23" xr:uid="{581132E9-940A-4066-B175-96156E8C3313}"/>
-    <hyperlink ref="A26" r:id="rId24" xr:uid="{92101F9D-3036-47FD-8BB7-4A7958529BA8}"/>
-    <hyperlink ref="A27" r:id="rId25" xr:uid="{32B70072-F9A0-4781-81AD-E183F9B7FA76}"/>
-    <hyperlink ref="A28" r:id="rId26" xr:uid="{98AFE265-349E-49B7-9301-86216BBABFD7}"/>
-    <hyperlink ref="A29" r:id="rId27" xr:uid="{5190D366-02F3-494B-A2B9-F7EA930CFDB6}"/>
-    <hyperlink ref="A30" r:id="rId28" xr:uid="{861C20A7-A608-4407-BF39-8C4836CB3EBA}"/>
-    <hyperlink ref="A31" r:id="rId29" xr:uid="{22B5E63D-5602-438D-A935-75CDB57BAA4F}"/>
-    <hyperlink ref="A32" r:id="rId30" xr:uid="{1531F536-DB40-4EB5-8ABB-0B088441FB80}"/>
-    <hyperlink ref="A33" r:id="rId31" xr:uid="{44BDC554-4FC2-4B5F-8E8B-94C71F9BFBF2}"/>
-    <hyperlink ref="A34" r:id="rId32" xr:uid="{4063819F-4F19-4D35-A46E-2918C0F0C2A9}"/>
-    <hyperlink ref="A35" r:id="rId33" xr:uid="{BBA10545-9F43-4886-95EB-B690DA824FF2}"/>
-    <hyperlink ref="A36" r:id="rId34" xr:uid="{2EB40A02-0757-48A2-827C-79A6DAB97C67}"/>
-    <hyperlink ref="A37" r:id="rId35" xr:uid="{C8ADDE1F-11DA-43C3-BB05-3188854D99EB}"/>
-    <hyperlink ref="A38" r:id="rId36" xr:uid="{0CF8A23D-6B09-444D-B6A5-A229904A3AA7}"/>
-    <hyperlink ref="A39" r:id="rId37" xr:uid="{51D397C3-2697-4EF4-96F6-69AF9B836452}"/>
-    <hyperlink ref="A40" r:id="rId38" xr:uid="{8AAB8322-BD12-40BE-80E7-7B4C90B340B9}"/>
-    <hyperlink ref="A41" r:id="rId39" xr:uid="{0CED4EA6-7AA0-443D-A01A-03C8949D29F1}"/>
-    <hyperlink ref="A42" r:id="rId40" xr:uid="{902C3609-C007-4D30-8CAB-8FD93C5BE407}"/>
-    <hyperlink ref="A43" r:id="rId41" xr:uid="{707CA654-C8B3-414D-AED1-0F983D1EE18E}"/>
-    <hyperlink ref="A44" r:id="rId42" xr:uid="{837507C2-9327-496B-BCB6-C10B30FEFB8B}"/>
-    <hyperlink ref="A45" r:id="rId43" xr:uid="{B60E5E83-AA8E-4B96-AD56-9F77FF82F58C}"/>
-    <hyperlink ref="A46" r:id="rId44" xr:uid="{AB768F19-B4C2-461A-BBFE-B14B95B05C3A}"/>
-    <hyperlink ref="A47" r:id="rId45" xr:uid="{C5A611E1-1B16-419A-B523-C417AA081523}"/>
-    <hyperlink ref="A48" r:id="rId46" xr:uid="{47850A40-EBF3-47A2-A573-C0D54222618A}"/>
-    <hyperlink ref="A49" r:id="rId47" xr:uid="{F10792E1-65EF-48D1-8AE0-9444B00016EF}"/>
-    <hyperlink ref="A50" r:id="rId48" xr:uid="{9DB36F24-A2DB-4C5C-9DBB-7D8A454A252F}"/>
-    <hyperlink ref="A51" r:id="rId49" xr:uid="{EE39BD8A-4D7C-4ACB-B2A0-134E4F8C99C2}"/>
-    <hyperlink ref="A52" r:id="rId50" xr:uid="{89D3F9B7-9F3C-4655-A97F-8282165E9FBA}"/>
-    <hyperlink ref="A53" r:id="rId51" xr:uid="{416B5964-F95D-41C0-A7EB-C7D869C748B3}"/>
-    <hyperlink ref="A54" r:id="rId52" xr:uid="{F410E308-05AB-49B7-8AC2-B82229989DC1}"/>
-    <hyperlink ref="A55" r:id="rId53" xr:uid="{C45C5FA6-EAFE-4A99-ADB2-6CAED6D7C469}"/>
-    <hyperlink ref="A56" r:id="rId54" xr:uid="{055A2CFB-C523-4E4D-B863-A39B733CBCFA}"/>
-    <hyperlink ref="A57" r:id="rId55" xr:uid="{2CF9B31F-F330-42B7-8AD0-CF8F3154A9B2}"/>
-    <hyperlink ref="A87" r:id="rId56" xr:uid="{340B4BE7-9A18-46FC-A93C-50C602622525}"/>
+    <hyperlink ref="A4" r:id="rId4" xr:uid="{4CB9E738-C2A3-4A0B-A76A-2BA6A3C71A0A}"/>
+    <hyperlink ref="A5" r:id="rId5" xr:uid="{808033F4-D4E3-455C-826E-285C2E7B7559}"/>
+    <hyperlink ref="A6" r:id="rId6" xr:uid="{CBDC038C-2AB8-4C78-927A-82ABF153C1F9}"/>
+    <hyperlink ref="A7" r:id="rId7" xr:uid="{33304A3B-055F-4AB5-BDE5-93C50D0B5A09}"/>
+    <hyperlink ref="A8" r:id="rId8" xr:uid="{A653D656-96D2-4E8B-A351-C084C18A7C41}"/>
+    <hyperlink ref="A9" r:id="rId9" xr:uid="{31A508E0-5F90-49AE-B561-5977B5C4F4CC}"/>
+    <hyperlink ref="A10" r:id="rId10" xr:uid="{69EFF606-7E4E-4758-8FBA-56C60A1C1E11}"/>
+    <hyperlink ref="A11" r:id="rId11" xr:uid="{B7A286A9-5428-4ACD-AB67-D0D27D4FF4B6}"/>
+    <hyperlink ref="A13" r:id="rId12" xr:uid="{D38AFE28-5C63-4B2A-9DE0-380E7FFAB029}"/>
+    <hyperlink ref="A14" r:id="rId13" xr:uid="{E690C1ED-6E53-467F-ADB5-85839B2A02C8}"/>
+    <hyperlink ref="A15" r:id="rId14" xr:uid="{FD31BAA3-A23D-488F-9251-4E9B3F823D1F}"/>
+    <hyperlink ref="A17" r:id="rId15" xr:uid="{E8734ADA-CBCA-4424-AB2A-4EF369BF37DC}"/>
+    <hyperlink ref="A18" r:id="rId16" xr:uid="{96D758A5-3ADE-45D8-9D94-184A169418CD}"/>
+    <hyperlink ref="A19" r:id="rId17" xr:uid="{7E513055-D324-4218-A278-3A0D89815E79}"/>
+    <hyperlink ref="A20" r:id="rId18" xr:uid="{45E02E90-651D-4B0F-894D-CC328F64B669}"/>
+    <hyperlink ref="A21" r:id="rId19" xr:uid="{D07FA495-029B-4B56-98E8-3D576F284893}"/>
+    <hyperlink ref="A22" r:id="rId20" xr:uid="{7E524225-DFAE-4D69-91F9-F781B31234C1}"/>
+    <hyperlink ref="A23" r:id="rId21" xr:uid="{FF41D14E-E8D4-4578-A644-05CC79649038}"/>
+    <hyperlink ref="A24" r:id="rId22" xr:uid="{581132E9-940A-4066-B175-96156E8C3313}"/>
+    <hyperlink ref="A25" r:id="rId23" xr:uid="{92101F9D-3036-47FD-8BB7-4A7958529BA8}"/>
+    <hyperlink ref="A26" r:id="rId24" xr:uid="{32B70072-F9A0-4781-81AD-E183F9B7FA76}"/>
+    <hyperlink ref="A27" r:id="rId25" xr:uid="{98AFE265-349E-49B7-9301-86216BBABFD7}"/>
+    <hyperlink ref="A28" r:id="rId26" xr:uid="{5190D366-02F3-494B-A2B9-F7EA930CFDB6}"/>
+    <hyperlink ref="A29" r:id="rId27" xr:uid="{861C20A7-A608-4407-BF39-8C4836CB3EBA}"/>
+    <hyperlink ref="A30" r:id="rId28" xr:uid="{22B5E63D-5602-438D-A935-75CDB57BAA4F}"/>
+    <hyperlink ref="A31" r:id="rId29" xr:uid="{1531F536-DB40-4EB5-8ABB-0B088441FB80}"/>
+    <hyperlink ref="A32" r:id="rId30" xr:uid="{44BDC554-4FC2-4B5F-8E8B-94C71F9BFBF2}"/>
+    <hyperlink ref="A33" r:id="rId31" xr:uid="{4063819F-4F19-4D35-A46E-2918C0F0C2A9}"/>
+    <hyperlink ref="A34" r:id="rId32" xr:uid="{BBA10545-9F43-4886-95EB-B690DA824FF2}"/>
+    <hyperlink ref="A35" r:id="rId33" xr:uid="{2EB40A02-0757-48A2-827C-79A6DAB97C67}"/>
+    <hyperlink ref="A36" r:id="rId34" xr:uid="{C8ADDE1F-11DA-43C3-BB05-3188854D99EB}"/>
+    <hyperlink ref="A37" r:id="rId35" xr:uid="{0CF8A23D-6B09-444D-B6A5-A229904A3AA7}"/>
+    <hyperlink ref="A38" r:id="rId36" xr:uid="{51D397C3-2697-4EF4-96F6-69AF9B836452}"/>
+    <hyperlink ref="A39" r:id="rId37" xr:uid="{8AAB8322-BD12-40BE-80E7-7B4C90B340B9}"/>
+    <hyperlink ref="A40" r:id="rId38" xr:uid="{0CED4EA6-7AA0-443D-A01A-03C8949D29F1}"/>
+    <hyperlink ref="A41" r:id="rId39" xr:uid="{902C3609-C007-4D30-8CAB-8FD93C5BE407}"/>
+    <hyperlink ref="A42" r:id="rId40" xr:uid="{707CA654-C8B3-414D-AED1-0F983D1EE18E}"/>
+    <hyperlink ref="A43" r:id="rId41" xr:uid="{837507C2-9327-496B-BCB6-C10B30FEFB8B}"/>
+    <hyperlink ref="A44" r:id="rId42" xr:uid="{B60E5E83-AA8E-4B96-AD56-9F77FF82F58C}"/>
+    <hyperlink ref="A45" r:id="rId43" xr:uid="{AB768F19-B4C2-461A-BBFE-B14B95B05C3A}"/>
+    <hyperlink ref="A46" r:id="rId44" xr:uid="{C5A611E1-1B16-419A-B523-C417AA081523}"/>
+    <hyperlink ref="A47" r:id="rId45" xr:uid="{47850A40-EBF3-47A2-A573-C0D54222618A}"/>
+    <hyperlink ref="A48" r:id="rId46" xr:uid="{F10792E1-65EF-48D1-8AE0-9444B00016EF}"/>
+    <hyperlink ref="A49" r:id="rId47" xr:uid="{9DB36F24-A2DB-4C5C-9DBB-7D8A454A252F}"/>
+    <hyperlink ref="A50" r:id="rId48" xr:uid="{EE39BD8A-4D7C-4ACB-B2A0-134E4F8C99C2}"/>
+    <hyperlink ref="A51" r:id="rId49" xr:uid="{89D3F9B7-9F3C-4655-A97F-8282165E9FBA}"/>
+    <hyperlink ref="A52" r:id="rId50" xr:uid="{416B5964-F95D-41C0-A7EB-C7D869C748B3}"/>
+    <hyperlink ref="A53" r:id="rId51" xr:uid="{F410E308-05AB-49B7-8AC2-B82229989DC1}"/>
+    <hyperlink ref="A54" r:id="rId52" xr:uid="{C45C5FA6-EAFE-4A99-ADB2-6CAED6D7C469}"/>
+    <hyperlink ref="A55" r:id="rId53" xr:uid="{055A2CFB-C523-4E4D-B863-A39B733CBCFA}"/>
+    <hyperlink ref="A56" r:id="rId54" xr:uid="{2CF9B31F-F330-42B7-8AD0-CF8F3154A9B2}"/>
+    <hyperlink ref="A85" r:id="rId55" xr:uid="{340B4BE7-9A18-46FC-A93C-50C602622525}"/>
+    <hyperlink ref="A75" r:id="rId56" xr:uid="{A575D697-B3A5-4394-B453-6DE295731BD8}"/>
+    <hyperlink ref="A72" r:id="rId57" xr:uid="{B65B27BF-D4AA-4245-B5E0-3EA839A1827E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
